--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F10" t="n">
-        <v>73983</v>
+        <v>110808</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 200股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,14 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>110808</v>
+        <v>147608</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 300股（平旧仓，无对应买入）</t>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
@@ -759,6 +759,33 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>仍买入未平仓 100股</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>688041</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>海光信息</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" t="n">
+        <v>67770.39999999999</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 200股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,45 +602,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300394</v>
+        <v>300750</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>25959</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>147608</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>300502</v>
+        <v>601208</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>100</v>
       </c>
       <c r="D8" t="n">
-        <v>60200</v>
+        <v>4850</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -656,38 +656,38 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>300548</v>
+        <v>688008</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>长芯博创</t>
+          <t>澜起科技</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>22006</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>73084.83</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>；仍卖出未平仓 300股</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>300750</v>
+        <v>688041</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,95 +697,14 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F10" t="n">
-        <v>147608</v>
+        <v>202243.99</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>601208</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>东材科技</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4850</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>688008</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>澜起科技</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>100</v>
-      </c>
-      <c r="D12" t="n">
-        <v>25442.23</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>仍买入未平仓 100股</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>688041</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>海光信息</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>200</v>
-      </c>
-      <c r="F13" t="n">
-        <v>67770.39999999999</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>；仍卖出未平仓 200股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,109 +602,136 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>300750</v>
+        <v>300502</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>57150</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>147608</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
+          <t>仍买入未平仓 100股</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>601208</v>
+        <v>300750</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>东材科技</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>4850</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>147608</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>688008</v>
+        <v>601208</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>东材科技</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>4850</v>
       </c>
       <c r="E9" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>73084.83</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>仅买入未平仓 100股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F10" t="n">
+        <v>73084.83</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 300股</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
         <v>688041</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>600</v>
-      </c>
-      <c r="F10" t="n">
-        <v>202243.99</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>；仍卖出未平仓 600股</t>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>400</v>
+      </c>
+      <c r="F11" t="n">
+        <v>134829.33</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 400股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
-        <v>57150</v>
+        <v>160876.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仍买入未平仓 100股</t>
+          <t>仍买入未平仓 300股</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,10 +502,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D3" t="n">
-        <v>6599</v>
+        <v>29995</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>仅买入未平仓 100股（跨期持有底仓）</t>
+          <t>仅买入未平仓 500股（跨期持有底仓）</t>
         </is>
       </c>
     </row>
@@ -683,11 +683,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688008</v>
+        <v>603920</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>世运电路</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -697,41 +697,95 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F10" t="n">
-        <v>73084.83</v>
+        <v>16355</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 300股</t>
+          <t>仅卖出未平仓 500股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
+        <v>688008</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>澜起科技</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" t="n">
+        <v>73084.83</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>；仍卖出未平仓 300股</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
         <v>688041</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>海光信息</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
         <v>400</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" t="n">
         <v>134829.33</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>；仍卖出未平仓 400股</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>688676</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>金盘科技</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>400</v>
+      </c>
+      <c r="F13" t="n">
+        <v>26788</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>仅卖出未平仓 400股（平旧仓，无对应买入）</t>
         </is>
       </c>
     </row>

--- a/reports/剩余持仓_2026-07.xlsx
+++ b/reports/剩余持仓_2026-07.xlsx
@@ -610,10 +610,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D7" t="n">
-        <v>160876.5</v>
+        <v>107251</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>仍买入未平仓 300股</t>
+          <t>仍买入未平仓 200股</t>
         </is>
       </c>
     </row>
@@ -751,14 +751,14 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="F12" t="n">
-        <v>134829.33</v>
+        <v>199423.52</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>；仍卖出未平仓 400股</t>
+          <t>；仍卖出未平仓 600股</t>
         </is>
       </c>
     </row>
